--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DFB490-BDDB-470D-9649-3CFB4F2265E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846573FB-AC15-4689-A35B-4C923390E254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="126">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -150,116 +150,6 @@
   </si>
   <si>
     <t>Informaţiile vor fi preluate din fişiere text.</t>
-  </si>
-  <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
-  </si>
-  <si>
-    <t>Observații</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
-  </si>
-  <si>
-    <t>addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
-  </si>
-  <si>
-    <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
-  </si>
-  <si>
-    <t>3. Se aleg doi parametri ai metodei testate şi se definesc condiţii asupra acestora. Condiţiile (constrângerile) rezultă din specificaţii.</t>
-  </si>
-  <si>
-    <t>4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Exemplu: Parametrii </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>title</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> şi </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">; Condiţii pentru aceşti parametri de intrare: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>title</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> este un string cu lungimea validă de la 1 la 255 caractere; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> este valid dacă ia valori între 1899 şi 2025.</t>
-    </r>
   </si>
   <si>
     <t>EC Identification</t>
@@ -647,12 +537,15 @@
   <si>
     <t>TC10_BVA</t>
   </si>
+  <si>
+    <t>Un proprietar de baruri doreste sa adauge o noua bautura.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -691,21 +584,6 @@
       <b/>
       <sz val="11"/>
       <color indexed="17"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="30"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color indexed="30"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1191,9 +1069,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1201,71 +1079,110 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1276,198 +1193,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1788,12 +1655,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="42"/>
       <c r="H1" s="26" t="s">
         <v>1</v>
       </c>
@@ -1801,11 +1668,11 @@
       <c r="J1" s="26"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
@@ -1821,7 +1688,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J4" s="2">
         <v>232</v>
@@ -1832,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J5" s="2">
         <v>232</v>
@@ -1876,7 +1743,7 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -1884,21 +1751,21 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38"/>
+      <c r="B16" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
@@ -1906,29 +1773,19 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
-        <v>12</v>
-      </c>
+      <c r="B18" s="24"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="B19" s="1"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="22" t="s">
-        <v>14</v>
-      </c>
+      <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B21" s="1"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="B22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1943,9 +1800,7 @@
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="B23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1961,21 +1816,19 @@
     </row>
     <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="23"/>
-      <c r="B24" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C26" s="25"/>
@@ -2016,153 +1869,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="38"/>
+      <c r="B3" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="G5" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
+      <c r="B5" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="G5" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="69"/>
+        <v>16</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" s="60"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>69</v>
+      <c r="C7" s="48" t="s">
+        <v>61</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7" s="72" t="s">
-        <v>85</v>
-      </c>
-      <c r="K7" s="72" t="s">
-        <v>86</v>
-      </c>
-      <c r="L7" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="N7" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" s="73"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="N7" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" s="63"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="33"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="72">
+        <v>63</v>
+      </c>
+      <c r="G8" s="27">
         <v>1</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I8" s="13">
         <v>10</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K8" s="13">
         <v>15</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="N8" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="O8" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="N8" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="56"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>72</v>
+      <c r="C9" s="48" t="s">
+        <v>64</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="72">
+      <c r="G9" s="27">
         <v>2</v>
       </c>
       <c r="H9" s="13">
@@ -2172,32 +2025,32 @@
         <v>-5</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K9" s="13">
         <v>15</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="N9" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="O9" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="N9" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="56"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="72">
+        <v>66</v>
+      </c>
+      <c r="G10" s="27">
         <v>3</v>
       </c>
       <c r="H10" s="13">
@@ -2207,34 +2060,34 @@
         <v>10</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K10" s="13">
         <v>-1</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="N10" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="O10" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="N10" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="O10" s="56"/>
     </row>
     <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>75</v>
+      <c r="C11" s="48" t="s">
+        <v>67</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="G11" s="72">
+      <c r="G11" s="27">
         <v>4</v>
       </c>
       <c r="H11" s="13">
@@ -2244,179 +2097,177 @@
         <v>10</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K11" s="13">
         <v>15</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="N11" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="O11" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="N11" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="O11" s="57"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="33"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="75"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
+        <v>69</v>
+      </c>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="34" t="s">
-        <v>78</v>
+      <c r="C13" s="49" t="s">
+        <v>70</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="76"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="77"/>
-      <c r="O13" s="77"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="35"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="75"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
-      <c r="N14" s="77"/>
-      <c r="O14" s="77"/>
+        <v>72</v>
+      </c>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>81</v>
+      <c r="C15" s="48" t="s">
+        <v>73</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E15" s="4"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="76"/>
-      <c r="M15" s="76"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="77"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="33"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="76"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="76"/>
-      <c r="N16" s="77"/>
-      <c r="O16" s="77"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="79"/>
-      <c r="C17" s="81"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="76"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="76"/>
-      <c r="K17" s="76"/>
-      <c r="L17" s="76"/>
-      <c r="M17" s="76"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="77"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="82"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="76"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="77"/>
-      <c r="O18" s="77"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="82"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="80"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="G19" s="11"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="82"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
+        <v>25</v>
+      </c>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="B1:E1"/>
@@ -2433,11 +2284,6 @@
     <mergeCell ref="N11:O11"/>
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="N9:O9"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="F22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2469,668 +2315,686 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="38"/>
+      <c r="B3" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
+      <c r="B5" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
+      <c r="G5" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
     </row>
     <row r="6" spans="2:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="G6" s="65" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="65" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="86"/>
-      <c r="P6" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="87"/>
+      <c r="G6" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="71"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="33">
+      <c r="B7" s="48">
         <v>1</v>
       </c>
-      <c r="C7" s="92" t="s">
-        <v>96</v>
+      <c r="C7" s="66" t="s">
+        <v>88</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="L7" s="72" t="s">
-        <v>85</v>
-      </c>
-      <c r="M7" s="88" t="s">
-        <v>86</v>
-      </c>
-      <c r="N7" s="88" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="P7" s="67" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q7" s="73"/>
+        <v>89</v>
+      </c>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q7" s="63"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="33"/>
-      <c r="C8" s="92"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="66"/>
       <c r="D8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="72">
+        <v>90</v>
+      </c>
+      <c r="G8" s="27">
         <v>1</v>
       </c>
       <c r="H8" s="8">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K8" s="13">
         <v>0</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="M8" s="13">
         <v>15</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P8" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q8" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="P8" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q8" s="56"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="33"/>
-      <c r="C9" s="92"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="66"/>
       <c r="D9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G9" s="72">
+        <v>91</v>
+      </c>
+      <c r="G9" s="27">
         <v>2</v>
       </c>
       <c r="H9" s="8">
         <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K9" s="12">
         <v>-1</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="M9" s="13">
         <v>15</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P9" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q9" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="P9" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q9" s="56"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="33"/>
-      <c r="C10" s="92"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="66"/>
       <c r="D10" s="2"/>
-      <c r="G10" s="72">
+      <c r="G10" s="27">
         <v>3</v>
       </c>
       <c r="H10" s="8">
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K10" s="12">
         <v>1</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="M10" s="13">
         <v>15</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P10" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q10" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="P10" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="56"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="33"/>
-      <c r="C11" s="92"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="66"/>
       <c r="D11" s="2"/>
-      <c r="G11" s="72">
+      <c r="G11" s="27">
         <v>4</v>
       </c>
       <c r="H11" s="8">
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K11" s="12">
         <v>10</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="M11" s="13">
         <v>0</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P11" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q11" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="P11" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q11" s="56"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="33"/>
-      <c r="C12" s="92"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="66"/>
       <c r="D12" s="2"/>
-      <c r="G12" s="72">
+      <c r="G12" s="27">
         <v>5</v>
       </c>
       <c r="H12" s="8">
         <v>5</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K12" s="12">
         <v>10</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="M12" s="13">
         <v>-0.01</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P12" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q12" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="P12" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q12" s="56"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="33">
+      <c r="B13" s="48">
         <v>2</v>
       </c>
-      <c r="C13" s="92" t="s">
-        <v>101</v>
+      <c r="C13" s="66" t="s">
+        <v>93</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G13" s="72">
+        <v>94</v>
+      </c>
+      <c r="G13" s="27">
         <v>6</v>
       </c>
       <c r="H13" s="8">
         <v>6</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K13" s="12">
         <v>10</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="M13" s="13">
         <v>0.01</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P13" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q13" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="P13" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q13" s="56"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14" s="72">
+        <v>95</v>
+      </c>
+      <c r="G14" s="27">
         <v>7</v>
       </c>
       <c r="H14" s="8">
         <v>7</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K14" s="12">
         <v>10</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="M14" s="13">
         <v>15</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P14" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q14" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="P14" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q14" s="56"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" s="72">
+        <v>96</v>
+      </c>
+      <c r="G15" s="27">
         <v>8</v>
       </c>
       <c r="H15" s="8">
         <v>8</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K15" s="12">
         <v>10</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="M15" s="13">
         <v>15</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P15" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q15" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="P15" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q15" s="56"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="2"/>
-      <c r="G16" s="72">
+      <c r="G16" s="27">
         <v>9</v>
       </c>
       <c r="H16" s="8">
         <v>9</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K16" s="12">
         <v>10</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="M16" s="13">
         <v>15</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P16" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q16" s="44"/>
+        <v>82</v>
+      </c>
+      <c r="P16" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q16" s="56"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="2"/>
-      <c r="G17" s="72">
+      <c r="G17" s="27">
         <v>10</v>
       </c>
       <c r="H17" s="8">
         <v>10</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K17" s="12">
         <v>10</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M17" s="13">
         <v>15</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="P17" s="83" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q17" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="P17" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q17" s="57"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
       <c r="D18" s="2"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="90"/>
-      <c r="J18" s="90"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="76"/>
-      <c r="O18" s="76"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="91"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B19" s="33">
+      <c r="B19" s="48">
         <v>3</v>
       </c>
-      <c r="C19" s="92" t="s">
+      <c r="C19" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="28"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B20" s="48"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="28"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B21" s="48"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" s="28"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B22" s="48"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G19" s="75"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="90"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="91"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B20" s="33"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G20" s="75"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="76"/>
-      <c r="N20" s="76"/>
-      <c r="O20" s="76"/>
-      <c r="P20" s="91"/>
-      <c r="Q20" s="91"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B21" s="33"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G21" s="75"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="90"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="76"/>
-      <c r="N21" s="76"/>
-      <c r="O21" s="76"/>
-      <c r="P21" s="91"/>
-      <c r="Q21" s="91"/>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="33"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" s="75"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="90"/>
-      <c r="J22" s="90"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="76"/>
-      <c r="O22" s="76"/>
-      <c r="P22" s="91"/>
-      <c r="Q22" s="91"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B23" s="33"/>
-      <c r="C23" s="92"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="66"/>
       <c r="D23" s="2"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="90"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="76"/>
-      <c r="O23" s="76"/>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="91"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="33"/>
-      <c r="C24" s="92"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="66"/>
       <c r="D24" s="2"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="90"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="76"/>
-      <c r="P24" s="91"/>
-      <c r="Q24" s="91"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="81"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="79"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="90"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
-      <c r="N25" s="76"/>
-      <c r="O25" s="76"/>
-      <c r="P25" s="91"/>
-      <c r="Q25" s="91"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="65"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="81"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="79"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="65"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="81"/>
-      <c r="C27" s="84"/>
-      <c r="D27" s="79"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="65"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="81"/>
-      <c r="C28" s="84"/>
-      <c r="D28" s="79"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="65"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
       <c r="N28" s="18"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B29" s="81"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="79"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="65"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
       <c r="N29" s="19"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="81"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="79"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -3147,30 +3011,6 @@
     <mergeCell ref="G5:Q5"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:M28"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3198,324 +3038,324 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
     </row>
     <row r="3" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B3" s="94" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
+      <c r="B3" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B4" s="95" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="95" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="69" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="68"/>
-      <c r="M4" s="74"/>
+      <c r="B4" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="62"/>
+      <c r="M4" s="76"/>
     </row>
     <row r="5" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="G5" s="72" t="s">
-        <v>85</v>
-      </c>
-      <c r="H5" s="72" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="69"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="60"/>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B6" s="72">
+      <c r="B6" s="27">
         <v>1</v>
       </c>
-      <c r="C6" s="100" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="98" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="98"/>
+      <c r="C6" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="35"/>
       <c r="F6" s="7">
         <v>10</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H6" s="7">
         <v>15</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K6" s="83" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K6" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="57"/>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B7" s="72">
+      <c r="B7" s="27">
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="100"/>
-      <c r="D7" s="98" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" s="98"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="35"/>
       <c r="F7" s="7">
         <v>-5</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H7" s="7">
         <v>15</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K7" s="83" t="s">
-        <v>91</v>
-      </c>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83" t="s">
-        <v>91</v>
-      </c>
-      <c r="N7" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K7" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="N7" s="57"/>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B8" s="72">
+      <c r="B8" s="27">
         <f t="shared" ref="B8:B13" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="98" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="98"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="35"/>
       <c r="F8" s="7">
         <v>10</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H8" s="7">
         <v>-1</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="83" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83" t="s">
-        <v>92</v>
-      </c>
-      <c r="N8" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K8" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8" s="57"/>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B9" s="72">
+      <c r="B9" s="27">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="100"/>
-      <c r="D9" s="98" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="98"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="35"/>
       <c r="F9" s="7">
         <v>10</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H9" s="7">
         <v>15</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="N9" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K9" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="N9" s="57"/>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B10" s="72">
+      <c r="B10" s="27">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="100"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98" t="s">
-        <v>126</v>
+      <c r="C10" s="74"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35" t="s">
+        <v>118</v>
       </c>
       <c r="F10" s="7">
         <v>0</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H10" s="7">
         <v>15</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K10" s="83" t="s">
-        <v>115</v>
-      </c>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83" t="s">
-        <v>115</v>
-      </c>
-      <c r="N10" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K10" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="N10" s="57"/>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B11" s="72">
+      <c r="B11" s="27">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="100"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98" t="s">
-        <v>127</v>
+      <c r="C11" s="74"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35" t="s">
+        <v>119</v>
       </c>
       <c r="F11" s="7">
         <v>-1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H11" s="7">
         <v>15</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K11" s="83" t="s">
-        <v>115</v>
-      </c>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83" t="s">
-        <v>115</v>
-      </c>
-      <c r="N11" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K11" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="N11" s="57"/>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B12" s="72">
+      <c r="B12" s="27">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="100"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98" t="s">
-        <v>52</v>
+      <c r="C12" s="74"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35" t="s">
+        <v>44</v>
       </c>
       <c r="F12" s="7">
         <v>1</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H12" s="7">
         <v>15</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K12" s="83" t="s">
-        <v>31</v>
-      </c>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K12" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="57"/>
       <c r="V12" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="W12" s="10"/>
       <c r="X12" s="11"/>
@@ -3525,260 +3365,260 @@
       <c r="AB12" s="5"/>
       <c r="AC12" s="5"/>
       <c r="AD12" s="5"/>
-      <c r="AE12" s="56"/>
-      <c r="AF12" s="56"/>
+      <c r="AE12" s="78"/>
+      <c r="AF12" s="78"/>
       <c r="AG12" s="5"/>
     </row>
     <row r="13" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="72">
+      <c r="B13" s="27">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="100"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98" t="s">
-        <v>53</v>
+      <c r="C13" s="74"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35" t="s">
+        <v>45</v>
       </c>
       <c r="F13" s="7">
         <v>10</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H13" s="7">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K13" s="83" t="s">
-        <v>116</v>
-      </c>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83" t="s">
-        <v>116</v>
-      </c>
-      <c r="N13" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K13" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="N13" s="57"/>
       <c r="AG13" s="5"/>
     </row>
     <row r="14" spans="2:36" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="72">
+      <c r="B14" s="27">
         <v>9</v>
       </c>
-      <c r="C14" s="100"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98" t="s">
-        <v>54</v>
+      <c r="C14" s="74"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35" t="s">
+        <v>46</v>
       </c>
       <c r="F14" s="7">
         <v>10</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H14" s="7">
         <v>-0.01</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K14" s="83" t="s">
-        <v>116</v>
-      </c>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83" t="s">
-        <v>116</v>
-      </c>
-      <c r="N14" s="83"/>
-      <c r="W14" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="X14" s="52"/>
-      <c r="Y14" s="52"/>
-      <c r="Z14" s="53"/>
+        <v>82</v>
+      </c>
+      <c r="K14" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="N14" s="57"/>
+      <c r="W14" s="84" t="s">
+        <v>48</v>
+      </c>
+      <c r="X14" s="85"/>
+      <c r="Y14" s="85"/>
+      <c r="Z14" s="86"/>
       <c r="AA14" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB14" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC14" s="51"/>
-      <c r="AD14" s="52"/>
-      <c r="AE14" s="52"/>
-      <c r="AF14" s="53"/>
-      <c r="AG14" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="AH14" s="51"/>
-      <c r="AI14" s="52"/>
-      <c r="AJ14" s="53"/>
+        <v>49</v>
+      </c>
+      <c r="AB14" s="84" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC14" s="87"/>
+      <c r="AD14" s="85"/>
+      <c r="AE14" s="85"/>
+      <c r="AF14" s="86"/>
+      <c r="AG14" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH14" s="87"/>
+      <c r="AI14" s="85"/>
+      <c r="AJ14" s="86"/>
     </row>
     <row r="15" spans="2:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="96">
+      <c r="B15" s="34">
         <v>10</v>
       </c>
-      <c r="C15" s="100"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="98" t="s">
-        <v>128</v>
+      <c r="C15" s="74"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="35" t="s">
+        <v>120</v>
       </c>
       <c r="F15" s="7">
         <v>10</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H15" s="7">
         <v>0.01</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K15" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="L15" s="83"/>
-      <c r="M15" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="N15" s="83"/>
-      <c r="V15" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="W15" s="101" t="s">
-        <v>60</v>
-      </c>
-      <c r="X15" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y15" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z15" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA15" s="63" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB15" s="59" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC15" s="60"/>
-      <c r="AD15" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE15" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF15" s="64" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG15" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH15" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI15" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ15" s="48" t="s">
-        <v>62</v>
+        <v>82</v>
+      </c>
+      <c r="K15" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="N15" s="57"/>
+      <c r="V15" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="W15" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="X15" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y15" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z15" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA15" s="92" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB15" s="88" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC15" s="89"/>
+      <c r="AD15" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE15" s="93" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF15" s="95" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG15" s="97" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH15" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI15" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ15" s="83" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B16" s="96">
+      <c r="B16" s="34">
         <v>11</v>
       </c>
-      <c r="C16" s="100"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="98" t="s">
-        <v>129</v>
+      <c r="C16" s="74"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="35" t="s">
+        <v>121</v>
       </c>
       <c r="F16" s="7">
         <v>10</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H16" s="7">
         <v>15</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K16" s="83" t="s">
-        <v>118</v>
-      </c>
-      <c r="L16" s="83"/>
-      <c r="M16" s="83" t="s">
-        <v>118</v>
-      </c>
-      <c r="N16" s="83"/>
-      <c r="V16" s="49"/>
-      <c r="W16" s="101"/>
-      <c r="X16" s="49"/>
-      <c r="Y16" s="49"/>
-      <c r="Z16" s="48"/>
-      <c r="AA16" s="63"/>
-      <c r="AB16" s="61"/>
-      <c r="AC16" s="62"/>
-      <c r="AD16" s="49"/>
-      <c r="AE16" s="42"/>
-      <c r="AF16" s="93"/>
-      <c r="AG16" s="55"/>
-      <c r="AH16" s="49"/>
-      <c r="AI16" s="49"/>
-      <c r="AJ16" s="48"/>
+        <v>82</v>
+      </c>
+      <c r="K16" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="N16" s="57"/>
+      <c r="V16" s="81"/>
+      <c r="W16" s="82"/>
+      <c r="X16" s="81"/>
+      <c r="Y16" s="81"/>
+      <c r="Z16" s="83"/>
+      <c r="AA16" s="92"/>
+      <c r="AB16" s="90"/>
+      <c r="AC16" s="91"/>
+      <c r="AD16" s="81"/>
+      <c r="AE16" s="94"/>
+      <c r="AF16" s="96"/>
+      <c r="AG16" s="98"/>
+      <c r="AH16" s="81"/>
+      <c r="AI16" s="81"/>
+      <c r="AJ16" s="83"/>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B17" s="97">
+      <c r="B17" s="27">
         <v>12</v>
       </c>
-      <c r="C17" s="100"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="98" t="s">
-        <v>130</v>
+      <c r="C17" s="74"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="35" t="s">
+        <v>122</v>
       </c>
       <c r="F17" s="7">
         <v>10</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H17" s="7">
         <v>15</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K17" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="L17" s="83"/>
-      <c r="M17" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="N17" s="83"/>
-      <c r="V17" s="103" t="s">
-        <v>49</v>
-      </c>
-      <c r="W17" s="102">
+        <v>82</v>
+      </c>
+      <c r="K17" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="N17" s="57"/>
+      <c r="V17" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="W17" s="37">
         <v>14</v>
       </c>
       <c r="X17" s="16">
@@ -3793,10 +3633,10 @@
       <c r="AA17" s="21">
         <v>1</v>
       </c>
-      <c r="AB17" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC17" s="58"/>
+      <c r="AB17" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC17" s="80"/>
       <c r="AD17" s="2">
         <v>1</v>
       </c>
@@ -3820,86 +3660,123 @@
       </c>
     </row>
     <row r="18" spans="2:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="97">
+      <c r="B18" s="27">
         <v>13</v>
       </c>
-      <c r="C18" s="100"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="98" t="s">
-        <v>131</v>
+      <c r="C18" s="74"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="35" t="s">
+        <v>123</v>
       </c>
       <c r="F18" s="7">
         <v>10</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H18" s="7">
         <v>15</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K18" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="L18" s="83"/>
-      <c r="M18" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="N18" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K18" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="N18" s="57"/>
     </row>
     <row r="19" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B19" s="97">
+      <c r="B19" s="27">
         <v>14</v>
       </c>
-      <c r="C19" s="100"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="98" t="s">
-        <v>132</v>
+      <c r="C19" s="74"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="35" t="s">
+        <v>124</v>
       </c>
       <c r="F19" s="7">
         <v>10</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H19" s="7">
         <v>15</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K19" s="83" t="s">
-        <v>119</v>
-      </c>
-      <c r="L19" s="83"/>
-      <c r="M19" s="83" t="s">
-        <v>119</v>
-      </c>
-      <c r="N19" s="83"/>
+        <v>82</v>
+      </c>
+      <c r="K19" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="N19" s="57"/>
     </row>
     <row r="21" spans="2:36" x14ac:dyDescent="0.25">
       <c r="K21" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="AI15:AI16"/>
+    <mergeCell ref="AJ15:AJ16"/>
+    <mergeCell ref="AG14:AJ14"/>
+    <mergeCell ref="AG15:AG16"/>
+    <mergeCell ref="AH15:AH16"/>
+    <mergeCell ref="AD15:AD16"/>
+    <mergeCell ref="W14:Z14"/>
+    <mergeCell ref="AB14:AF14"/>
+    <mergeCell ref="AB15:AC16"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="AE15:AE16"/>
+    <mergeCell ref="AF15:AF16"/>
+    <mergeCell ref="AB17:AC17"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="B4:B5"/>
     <mergeCell ref="M18:N18"/>
     <mergeCell ref="M19:N19"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="C6:C19"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="M11:N11"/>
@@ -3911,45 +3788,8 @@
     <mergeCell ref="M17:N17"/>
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="AB17:AC17"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="X15:X16"/>
-    <mergeCell ref="Y15:Y16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="AD15:AD16"/>
-    <mergeCell ref="W14:Z14"/>
-    <mergeCell ref="AB14:AF14"/>
-    <mergeCell ref="AB15:AC16"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="AE15:AE16"/>
-    <mergeCell ref="AF15:AF16"/>
-    <mergeCell ref="AI15:AI16"/>
-    <mergeCell ref="AJ15:AJ16"/>
-    <mergeCell ref="AG14:AJ14"/>
-    <mergeCell ref="AG15:AG16"/>
-    <mergeCell ref="AH15:AH16"/>
   </mergeCells>
-  <phoneticPr fontId="22" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -3957,6 +3797,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4094,22 +3949,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4125,21 +3982,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>